--- a/output/pdf_financials_xlsx/FCI.xlsx
+++ b/output/pdf_financials_xlsx/FCI.xlsx
@@ -1167,7 +1167,7 @@
         <v>-0.898602</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.419675</v>
+        <v>-0.419675</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.165339</v>
@@ -1191,10 +1191,10 @@
         <v>-2.445801</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.241146</v>
+        <v>-3.241146</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.784254</v>
+        <v>-1.784254</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-1.915478</v>
@@ -1423,7 +1423,7 @@
         <v>-0.898602</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.419675</v>
+        <v>-0.419675</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.165339</v>
@@ -1447,10 +1447,10 @@
         <v>-2.445801</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.241146</v>
+        <v>-3.241146</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.784254</v>
+        <v>-1.784254</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-1.915478</v>
@@ -1576,7 +1576,7 @@
         <v>-0.898602</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.419675</v>
+        <v>-0.419675</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.165339</v>
@@ -1600,10 +1600,10 @@
         <v>-2.445801</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.241146</v>
+        <v>-3.241146</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.784254</v>
+        <v>-1.784254</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-1.915478</v>
@@ -1729,7 +1729,7 @@
         <v>12.837171</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-20.98375</v>
+        <v>20.98375</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>5.549233</v>
@@ -1753,10 +1753,10 @@
         <v>61.145025</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-64.82292</v>
+        <v>64.82292</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-8.110245000000001</v>
+        <v>8.110245000000001</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>10.641544</v>
@@ -1780,7 +1780,7 @@
         <v>-0.898602</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.419675</v>
+        <v>-0.419675</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.165339</v>
@@ -1804,10 +1804,10 @@
         <v>-2.445801</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.241146</v>
+        <v>-3.241146</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.784254</v>
+        <v>-1.784254</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-1.915478</v>
@@ -1882,7 +1882,7 @@
         <v>-0.898602</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.419675</v>
+        <v>-0.419675</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.165339</v>
@@ -1906,10 +1906,10 @@
         <v>-2.445801</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.241146</v>
+        <v>-3.241146</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.784254</v>
+        <v>-1.784254</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.915478</v>
@@ -2010,7 +2010,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2034,10 +2034,10 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -5131,13 +5131,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.955725</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.955725</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.992333</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>2.014645</v>
@@ -11844,7 +11844,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -12786,7 +12790,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>1.955725</v>
       </c>
@@ -22276,13 +22284,13 @@
         </is>
       </c>
       <c r="O178" s="5" t="n">
-        <v>3.241146</v>
+        <v>-3.241146</v>
       </c>
       <c r="P178" s="5" t="n">
-        <v>1.784254</v>
+        <v>-1.784254</v>
       </c>
       <c r="Q178" s="5" t="n">
-        <v>1.915478</v>
+        <v>-1.915478</v>
       </c>
       <c r="R178" t="inlineStr">
         <is>
@@ -36762,10 +36770,10 @@
         <v>-0.898602</v>
       </c>
       <c r="G348" s="5" t="n">
-        <v>0.419675</v>
+        <v>-0.419675</v>
       </c>
       <c r="H348" s="5" t="n">
-        <v>1.165339</v>
+        <v>-1.165339</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FCI.xlsx
+++ b/output/pdf_financials_xlsx/FCI.xlsx
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-8.500000000000001e-05</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>-3.241146</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.784254</v>
+        <v>-1.784169</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-1.915478</v>
@@ -1909,7 +1909,7 @@
         <v>-3.241146</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.784254</v>
+        <v>-1.784169</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.915478</v>
@@ -2137,46 +2137,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.015308</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002452</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001183</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000857</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.532703</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.779234</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.200266</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.110896</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.874227</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.200504</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.787954</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.240175</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.293468</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.690781</v>
       </c>
     </row>
     <row r="35">
@@ -2235,46 +2235,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.015308</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002452</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001183</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000857</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.532703</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.779234</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.200266</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.110896</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.874227</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.200504</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.787954</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.240175</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.293468</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.690781</v>
       </c>
     </row>
     <row r="37">
@@ -2823,46 +2823,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.017358</v>
+        <v>0.00205</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.005302</v>
+        <v>0.00285</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.007325</v>
+        <v>0.006142</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.019068</v>
+        <v>0.018211</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.568291</v>
+        <v>0.035588</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.923774</v>
+        <v>0.14454</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.430116</v>
+        <v>0.22985</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.141041</v>
+        <v>0.030145</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.04013</v>
+        <v>0.165903</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.670694</v>
+        <v>0.47019</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.831673</v>
+        <v>0.043719</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.254041</v>
+        <v>0.013866</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.331343</v>
+        <v>0.037875</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.738725</v>
+        <v>0.047944</v>
       </c>
     </row>
     <row r="49">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">

--- a/output/pdf_financials_xlsx/FCI.xlsx
+++ b/output/pdf_financials_xlsx/FCI.xlsx
@@ -16292,7 +16292,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
